--- a/rosnedra_forecast/2026/rosnedra_page8.xlsx
+++ b/rosnedra_forecast/2026/rosnedra_page8.xlsx
@@ -420,7 +420,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
@@ -443,7 +443,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Извлекаемые запасы и природные ресурсы (с указанием категории) (ед.изм)</t>
+          <t>Извлекаемые запасы и прогнозные ресурсы</t>
         </is>
       </c>
     </row>
@@ -453,18 +453,19 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Удмуртская Республика</t>
+          <t>Ульяновская область</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Карсовайский участок</t>
+          <t>Старокулаткинский участок</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-D0 - 1,642 млн т</t>
+          <t>нефть (геол./извл.):
+C1 - 0,531/0,133 млн.т
+D0 - 0,964/0,241 млн.т</t>
         </is>
       </c>
     </row>
@@ -474,18 +475,22 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Удмуртская Республика</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Южно-Киенгопский участок</t>
+          <t>Тарховский</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-D0 - 1,944 млн т</t>
+          <t>нефть (геол./извл.):
+A - 0,856/0,056 млн.т
+B1 - 1,056/0,257 млн.т
+D0 - 0,380/0,091 млн.т
+D1 - 2,704/0,891 млн.т
+D2 - 13,471/2,021 млн.т</t>
         </is>
       </c>
     </row>
@@ -495,18 +500,21 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Ульяновская область</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Южно-Репьевский</t>
+          <t>Турьяхский</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 0,478/0,143 млн т</t>
+          <t>нефть (извл.):
+D0 - 5,802 млн.т
+Dл - 2,032 млн.т
+D1 - 3,283 млн.т
+D2 - 3,973 млн.т</t>
         </is>
       </c>
     </row>
@@ -516,20 +524,21 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Имилорский</t>
+          <t>Южно-Чистинный 1</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-C1 - 9,154 млн т
-газ (извл.):
-C1 - 1,173 млрд м3</t>
+D0 - 5,835 млн.т
+Dл - 1,291 млн.т
+D1 - 7,461 млн.т
+D2 - 2,947 млн.т</t>
         </is>
       </c>
     </row>
@@ -539,20 +548,21 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Западно-Имилорский</t>
+          <t>Южно-Чистинный 2</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-C1 - 3,784 млн т
-газ (извл.):
-C1 - 0,486 млрд м3</t>
+D0 - 13,933 млн.т
+Dл - 6,826 млн.т
+D1 - 6,597 млн.т
+D2 - 1,622 млн.т</t>
         </is>
       </c>
     </row>
@@ -562,20 +572,21 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Северо-Имилорский</t>
+          <t>Южно-Чистинный 3</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-C1 - 4,265 млн т
-газ (извл.):
-C1 - 0,548 млрд м3</t>
+D0 - 6,482 млн.т
+Dл - 1,438 млн.т
+D1 - 4,266 млн.т
+D2 - 1,774 млн.т</t>
         </is>
       </c>
     </row>
@@ -585,20 +596,21 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Западно-Салымский</t>
+          <t>Юильский 1</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 15,417/4,625 млн т
-газ (геол./извл.):
-D1 - 1,024/1,024 млрд м3</t>
+          <t>нефть (извл.):
+D1 - 4,0 млн.т
+D2 - 1,3 млн.т
+газ (извл.):
+D2 - 1,3 млрд.м3</t>
         </is>
       </c>
     </row>
@@ -608,20 +620,20 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Южно-Салымский</t>
+          <t>Млечный</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
           <t>нефть (геол./извл.):
-D1 - 11,328/3,398 млн т
-газ (геол./извл.):
-D1 - 0,752/0,752 млрд м3</t>
+A - 0,464/0,133 млн.т
+B1 - 0,556/0,194 млн.т
+B2 - 2,784/0,852 млн.т</t>
         </is>
       </c>
     </row>
@@ -631,20 +643,19 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Ханты-Мансийский автономный округ-Югра</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Восточно-Салымский</t>
+          <t>Северо-Салымский - 3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 13,806/4,142 млн т
-газ (геол./извл.):
-D1 - 0,916/0,916 млрд м3</t>
+          <t>нефть (извл.):
+D1 - 0,433 млн.т
+D2 - 0,168 млн.т</t>
         </is>
       </c>
     </row>
